--- a/data/trans_dic/P32D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 15,17</t>
+          <t>7,76; 15,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 14,56</t>
+          <t>3,19; 14,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,32</t>
+          <t>7,72; 14,01</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,61</t>
+          <t>7,4; 11,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,08</t>
+          <t>1,25; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,49</t>
+          <t>4,41; 8,45</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,4</t>
+          <t>4,89; 10,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 15,44</t>
+          <t>7,0; 15,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,54</t>
+          <t>6,5; 11,39</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,04</t>
+          <t>7,66; 10,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,49</t>
+          <t>2,65; 7,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,01</t>
+          <t>5,79; 9,11</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19320; 36434</t>
+          <t>18632; 37162</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2180; 9607</t>
+          <t>2108; 9540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22964; 43847</t>
+          <t>23648; 42907</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72924; 114085</t>
+          <t>72682; 115345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8654; 35974</t>
+          <t>8825; 38662</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72893; 143673</t>
+          <t>74557; 142975</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16401; 35555</t>
+          <t>16713; 35992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17403; 37820</t>
+          <t>17150; 38869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38389; 67752</t>
+          <t>38144; 66846</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121201; 172826</t>
+          <t>119882; 168844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25872; 76327</t>
+          <t>26976; 74364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149218; 232982</t>
+          <t>149642; 235327</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,47</t>
+          <t>8,22; 16,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,46</t>
+          <t>3,85; 17,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,01</t>
+          <t>7,63; 14,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,74</t>
+          <t>7,85; 12,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,46</t>
+          <t>3,75; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,45</t>
+          <t>6,91; 10,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,52</t>
+          <t>4,9; 10,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 15,87</t>
+          <t>6,82; 15,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,39</t>
+          <t>6,4; 11,34</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,79</t>
+          <t>8,02; 11,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,29</t>
+          <t>5,47; 9,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,11</t>
+          <t>7,67; 10,18</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>34993</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18632; 37162</t>
+          <t>20929; 42115</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2108; 9540</t>
+          <t>2831; 12512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23648; 42907</t>
+          <t>25030; 47033</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91591</t>
+          <t>104541</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114540</t>
+          <t>134599</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72682; 115345</t>
+          <t>82013; 130964</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8825; 38662</t>
+          <t>20970; 43266</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74557; 142975</t>
+          <t>110873; 162380</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>54495</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16713; 35992</t>
+          <t>17912; 37927</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17150; 38869</t>
+          <t>18313; 41526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38144; 66846</t>
+          <t>40556; 71865</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>143949</t>
+          <t>160624</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54079</t>
+          <t>63463</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198028</t>
+          <t>224087</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>119882; 168844</t>
+          <t>133499; 189379</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26976; 74364</t>
+          <t>49325; 81220</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149642; 235327</t>
+          <t>196806; 261321</t>
         </is>
       </c>
     </row>
